--- a/tests/fixtures/orderforms/1508.36.tomte.xlsx
+++ b/tests/fixtures/orderforms/1508.36.tomte.xlsx
@@ -5,10 +5,10 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isakohlsson/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isakohlsson/dev/cg/tests/fixtures/orderforms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F0CB2FF-CE6F-4B44-8891-23D3DE78D0A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA4F626-6036-C244-8024-2CDEA5B561EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="500" windowWidth="51200" windowHeight="28300" tabRatio="993" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15723,7 +15723,7 @@
         <v>722</v>
       </c>
       <c r="F17" s="67" t="s">
-        <v>712</v>
+        <v>462</v>
       </c>
       <c r="G17" s="68" t="s">
         <v>80</v>
@@ -16782,7 +16782,7 @@
         <v>729</v>
       </c>
       <c r="F18" s="67" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G18" s="68" t="s">
         <v>80</v>
@@ -17841,7 +17841,7 @@
         <v>732</v>
       </c>
       <c r="F19" s="67" t="s">
-        <v>460</v>
+        <v>551</v>
       </c>
       <c r="G19" s="68" t="s">
         <v>80</v>
@@ -18900,7 +18900,7 @@
         <v>735</v>
       </c>
       <c r="F20" s="67" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="G20" s="68" t="s">
         <v>80</v>
@@ -19959,7 +19959,7 @@
         <v>738</v>
       </c>
       <c r="F21" s="67" t="s">
-        <v>712</v>
+        <v>460</v>
       </c>
       <c r="G21" s="68" t="s">
         <v>80</v>
@@ -21018,7 +21018,7 @@
         <v>741</v>
       </c>
       <c r="F22" s="67" t="s">
-        <v>462</v>
+        <v>551</v>
       </c>
       <c r="G22" s="68" t="s">
         <v>80</v>
@@ -22077,7 +22077,7 @@
         <v>744</v>
       </c>
       <c r="F23" s="67" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G23" s="68" t="s">
         <v>80</v>
@@ -23136,7 +23136,7 @@
         <v>747</v>
       </c>
       <c r="F24" s="67" t="s">
-        <v>551</v>
+        <v>460</v>
       </c>
       <c r="G24" s="68" t="s">
         <v>80</v>
@@ -24195,7 +24195,7 @@
         <v>750</v>
       </c>
       <c r="F25" s="67" t="s">
-        <v>712</v>
+        <v>551</v>
       </c>
       <c r="G25" s="68" t="s">
         <v>80</v>
@@ -27442,7 +27442,7 @@
         <v>762</v>
       </c>
       <c r="F29" s="67" t="s">
-        <v>712</v>
+        <v>462</v>
       </c>
       <c r="G29" s="68" t="s">
         <v>80</v>
@@ -28501,7 +28501,7 @@
         <v>765</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G30" s="68" t="s">
         <v>80</v>
@@ -29560,7 +29560,7 @@
         <v>768</v>
       </c>
       <c r="F31" s="67" t="s">
-        <v>460</v>
+        <v>551</v>
       </c>
       <c r="G31" s="68" t="s">
         <v>80</v>
@@ -30619,7 +30619,7 @@
         <v>771</v>
       </c>
       <c r="F32" s="67" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="G32" s="68" t="s">
         <v>80</v>
@@ -31678,7 +31678,7 @@
         <v>774</v>
       </c>
       <c r="F33" s="67" t="s">
-        <v>712</v>
+        <v>460</v>
       </c>
       <c r="G33" s="68" t="s">
         <v>80</v>
@@ -32737,7 +32737,7 @@
         <v>777</v>
       </c>
       <c r="F34" s="67" t="s">
-        <v>462</v>
+        <v>551</v>
       </c>
       <c r="G34" s="68" t="s">
         <v>80</v>
@@ -33796,7 +33796,7 @@
         <v>780</v>
       </c>
       <c r="F35" s="67" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G35" s="68" t="s">
         <v>80</v>
@@ -34855,7 +34855,7 @@
         <v>783</v>
       </c>
       <c r="F36" s="67" t="s">
-        <v>551</v>
+        <v>460</v>
       </c>
       <c r="G36" s="68" t="s">
         <v>80</v>
@@ -34925,7 +34925,7 @@
         <v>786</v>
       </c>
       <c r="F37" s="67" t="s">
-        <v>712</v>
+        <v>551</v>
       </c>
       <c r="G37" s="68" t="s">
         <v>80</v>
@@ -37183,7 +37183,7 @@
         <v>798</v>
       </c>
       <c r="F41" s="67" t="s">
-        <v>712</v>
+        <v>462</v>
       </c>
       <c r="G41" s="68" t="s">
         <v>80</v>
@@ -38242,7 +38242,7 @@
         <v>801</v>
       </c>
       <c r="F42" s="67" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G42" s="68" t="s">
         <v>80</v>
@@ -39301,7 +39301,7 @@
         <v>804</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>460</v>
+        <v>551</v>
       </c>
       <c r="G43" s="68" t="s">
         <v>80</v>
@@ -40360,7 +40360,7 @@
         <v>807</v>
       </c>
       <c r="F44" s="67" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="G44" s="68" t="s">
         <v>80</v>
@@ -41419,7 +41419,7 @@
         <v>810</v>
       </c>
       <c r="F45" s="67" t="s">
-        <v>712</v>
+        <v>460</v>
       </c>
       <c r="G45" s="68" t="s">
         <v>80</v>
@@ -42478,7 +42478,7 @@
         <v>813</v>
       </c>
       <c r="F46" s="67" t="s">
-        <v>462</v>
+        <v>551</v>
       </c>
       <c r="G46" s="68" t="s">
         <v>80</v>
@@ -43537,7 +43537,7 @@
         <v>816</v>
       </c>
       <c r="F47" s="67" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G47" s="68" t="s">
         <v>80</v>
@@ -44596,7 +44596,7 @@
         <v>819</v>
       </c>
       <c r="F48" s="67" t="s">
-        <v>551</v>
+        <v>460</v>
       </c>
       <c r="G48" s="68" t="s">
         <v>80</v>
@@ -45655,7 +45655,7 @@
         <v>822</v>
       </c>
       <c r="F49" s="67" t="s">
-        <v>712</v>
+        <v>551</v>
       </c>
       <c r="G49" s="68" t="s">
         <v>80</v>
@@ -48902,7 +48902,7 @@
         <v>834</v>
       </c>
       <c r="F53" s="67" t="s">
-        <v>712</v>
+        <v>462</v>
       </c>
       <c r="G53" s="68" t="s">
         <v>80</v>
@@ -49961,7 +49961,7 @@
         <v>837</v>
       </c>
       <c r="F54" s="67" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G54" s="68" t="s">
         <v>80</v>
@@ -51020,7 +51020,7 @@
         <v>840</v>
       </c>
       <c r="F55" s="67" t="s">
-        <v>460</v>
+        <v>551</v>
       </c>
       <c r="G55" s="68" t="s">
         <v>80</v>
@@ -52079,7 +52079,7 @@
         <v>843</v>
       </c>
       <c r="F56" s="67" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="G56" s="68" t="s">
         <v>80</v>
